--- a/Brazil/data/dataset.xlsx
+++ b/Brazil/data/dataset.xlsx
@@ -49,6 +49,9 @@
     <t>ANBIMA12_IBVSP12</t>
   </si>
   <si>
+    <t xml:space="preserve">Moeda, Crédito e Mercado Financeiro</t>
+  </si>
+  <si>
     <t xml:space="preserve">Poupança - rentabilidade</t>
   </si>
   <si>
@@ -58,15 +61,15 @@
     <t>ANP12_CALCO12</t>
   </si>
   <si>
+    <t xml:space="preserve">Contas Nacionais e Nível de Atividade Econômica</t>
+  </si>
+  <si>
     <t xml:space="preserve">Consumo derivados Petróleo</t>
   </si>
   <si>
     <t>ANP12_CDEPET12</t>
   </si>
   <si>
-    <t xml:space="preserve">Contas Nacionais</t>
-  </si>
-  <si>
     <t xml:space="preserve">Consumo aparente - Gasolina</t>
   </si>
   <si>
@@ -100,15 +103,15 @@
     <t>BM12_DEVM12</t>
   </si>
   <si>
-    <t xml:space="preserve">Moeda e Crédito</t>
-  </si>
-  <si>
     <t xml:space="preserve">DLSP - dívida externa líquida - estados e municípios</t>
   </si>
   <si>
     <t>BM12_DEXEMN12</t>
   </si>
   <si>
+    <t xml:space="preserve">Finanças Públicas</t>
+  </si>
+  <si>
     <t xml:space="preserve">DLSP - dívida externa líquida - governo federal e Banco Central</t>
   </si>
   <si>
@@ -145,7 +148,7 @@
     <t>BM12_ERC12</t>
   </si>
   <si>
-    <t>Câmbio</t>
+    <t xml:space="preserve">Balanço de Pagamentos, Câmbio e Comércio Exterior</t>
   </si>
   <si>
     <t xml:space="preserve">IPCA - preços livres - comercializáveis</t>
@@ -154,6 +157,9 @@
     <t>BM12_IPCACOM12</t>
   </si>
   <si>
+    <t xml:space="preserve">Inflação e Nível de Preços</t>
+  </si>
+  <si>
     <t xml:space="preserve">IPCA - preços livres -não comercializáveis</t>
   </si>
   <si>
@@ -220,9 +226,6 @@
     <t>BM12_RES12</t>
   </si>
   <si>
-    <t xml:space="preserve">Balanço de Pagamentos</t>
-  </si>
-  <si>
     <t xml:space="preserve">Ouro - rendimento nominal</t>
   </si>
   <si>
@@ -289,6 +292,9 @@
     <t>CNI12_PEEMP12</t>
   </si>
   <si>
+    <t xml:space="preserve">Mercado de Trabalho e Renda</t>
+  </si>
+  <si>
     <t>ICMS</t>
   </si>
   <si>
@@ -301,18 +307,12 @@
     <t>DIMAC_ECFLIQTOT12</t>
   </si>
   <si>
-    <t xml:space="preserve">Estoque de Capital</t>
-  </si>
-  <si>
     <t xml:space="preserve">Consumo Energia Comércio</t>
   </si>
   <si>
     <t>ELETRO12_CEECOM12</t>
   </si>
   <si>
-    <t xml:space="preserve">Consumo e Vendas</t>
-  </si>
-  <si>
     <t xml:space="preserve">Consumo Energia Industria</t>
   </si>
   <si>
@@ -349,6 +349,9 @@
     <t>FCESP12_IIC12</t>
   </si>
   <si>
+    <t xml:space="preserve">Expectativas e Confiança</t>
+  </si>
+  <si>
     <t xml:space="preserve">Índice de Condições Econômicas Atuais</t>
   </si>
   <si>
@@ -397,9 +400,6 @@
     <t>FIRJAN12_EINDRJ12</t>
   </si>
   <si>
-    <t>Emprego</t>
-  </si>
-  <si>
     <t>FIRJAN12_FATREALRJ12</t>
   </si>
   <si>
@@ -415,9 +415,6 @@
     <t>FUNCEX12_MDPT12</t>
   </si>
   <si>
-    <t xml:space="preserve">Comércio Exterior</t>
-  </si>
-  <si>
     <t>Import_cons_duravel</t>
   </si>
   <si>
@@ -869,6 +866,9 @@
   </si>
   <si>
     <t>PRECOS12_IPCA12</t>
+  </si>
+  <si>
+    <t>AR</t>
   </si>
 </sst>
 </file>
@@ -882,7 +882,6 @@
   <fonts count="2">
     <font>
       <sz val="11.000000"/>
-      <color indexed="64"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -917,7 +916,7 @@
     <xf fontId="1" fillId="0" borderId="0" numFmtId="42" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0"/>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyProtection="0">
       <protection hidden="0" locked="1"/>
     </xf>
@@ -929,6 +928,9 @@
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1" applyProtection="1">
       <alignment wrapText="1"/>
+      <protection hidden="0" locked="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyProtection="1">
       <protection hidden="0" locked="1"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="165" xfId="0" applyNumberFormat="1" applyProtection="1">
@@ -954,8 +956,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" displayName="Tabela1" ref="A1:G141" headerRowCount="1" totalsRowCount="0">
-  <autoFilter ref="A1:G141"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" displayName="Tabela1" ref="A1:G142" headerRowCount="1" totalsRowCount="0">
+  <autoFilter ref="A1:G142"/>
   <tableColumns count="7">
     <tableColumn id="1" name="nome"/>
     <tableColumn id="2" name="fonte"/>
@@ -1436,7 +1438,7 @@
     <col customWidth="1" min="4" max="4" style="1" width="10.42"/>
     <col customWidth="1" min="5" max="5" style="1" width="10.550000000000001"/>
     <col customWidth="1" min="6" max="6" style="1" width="16.43"/>
-    <col customWidth="1" min="7" max="7" style="1" width="22.289999999999999"/>
+    <col customWidth="1" min="7" max="7" style="1" width="48.7109375"/>
   </cols>
   <sheetData>
     <row r="1" ht="15">
@@ -1481,33 +1483,42 @@
       <c r="F2" s="1">
         <v>1</v>
       </c>
+      <c r="G2" s="1" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="3" ht="15">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
+      <c r="G3" s="1" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="4" ht="15">
       <c r="C4" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
+      <c r="G4" s="1" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="5" ht="15">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D5" s="2">
         <v>32874</v>
@@ -1519,18 +1530,18 @@
         <v>1</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" ht="15">
       <c r="A6" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D6" s="2">
         <v>32874</v>
@@ -1542,18 +1553,18 @@
         <v>1</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" ht="15">
       <c r="A7" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D7" s="2">
         <v>32874</v>
@@ -1565,39 +1576,48 @@
         <v>1</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8" ht="15">
       <c r="C8" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
+      <c r="G8" s="1" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="9" ht="15">
       <c r="C9" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
+      <c r="G9" s="1" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="10" ht="15">
       <c r="C10" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
+      <c r="G10" s="1" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="11" ht="15">
       <c r="A11" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D11" s="2">
         <v>32874</v>
@@ -1608,16 +1628,19 @@
       <c r="F11" s="1">
         <v>1</v>
       </c>
+      <c r="G11" s="1" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="12" ht="15">
       <c r="A12" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D12" s="2">
         <v>29495</v>
@@ -1629,7 +1652,7 @@
         <v>1</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" ht="15">
@@ -1651,16 +1674,19 @@
       <c r="F13" s="1">
         <v>1</v>
       </c>
+      <c r="G13" s="1" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="14" ht="15">
       <c r="A14" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D14" s="2">
         <v>32874</v>
@@ -1671,16 +1697,19 @@
       <c r="F14" s="1">
         <v>1</v>
       </c>
+      <c r="G14" s="1" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="15" ht="15">
       <c r="A15" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D15" s="2">
         <v>32874</v>
@@ -1691,16 +1720,19 @@
       <c r="F15" s="1">
         <v>1</v>
       </c>
+      <c r="G15" s="1" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="16" ht="15">
       <c r="A16" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D16" s="2">
         <v>32874</v>
@@ -1711,16 +1743,19 @@
       <c r="F16" s="1">
         <v>1</v>
       </c>
+      <c r="G16" s="1" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="17" ht="15">
       <c r="A17" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D17" s="2">
         <v>32874</v>
@@ -1731,16 +1766,19 @@
       <c r="F17" s="1">
         <v>1</v>
       </c>
+      <c r="G17" s="1" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="18" ht="15">
       <c r="A18" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D18" s="2">
         <v>32874</v>
@@ -1751,16 +1789,19 @@
       <c r="F18" s="1">
         <v>1</v>
       </c>
+      <c r="G18" s="1" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="19" ht="15">
       <c r="A19" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D19" s="2">
         <v>32874</v>
@@ -1772,18 +1813,18 @@
         <v>1</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="20" ht="15">
       <c r="A20" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D20" s="2">
         <v>29495</v>
@@ -1793,37 +1834,43 @@
       </c>
       <c r="F20" s="1">
         <v>1</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="21" ht="15">
       <c r="A21" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C21" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D21" s="2">
+        <v>29495</v>
+      </c>
+      <c r="E21" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F21" s="1">
+        <v>1</v>
+      </c>
+      <c r="G21" s="1" t="s">
         <v>46</v>
-      </c>
-      <c r="D21" s="2">
-        <v>29495</v>
-      </c>
-      <c r="E21" s="2">
-        <v>45657</v>
-      </c>
-      <c r="F21" s="1">
-        <v>1</v>
       </c>
     </row>
     <row r="22" ht="15">
       <c r="A22" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D22" s="2">
         <v>29495</v>
@@ -1833,17 +1880,20 @@
       </c>
       <c r="F22" s="1">
         <v>1</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="23" ht="15">
       <c r="A23" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D23" s="2">
         <v>29495</v>
@@ -1853,17 +1903,20 @@
       </c>
       <c r="F23" s="1">
         <v>1</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="24" ht="15">
       <c r="A24" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D24" s="2">
         <v>29495</v>
@@ -1873,17 +1926,20 @@
       </c>
       <c r="F24" s="1">
         <v>1</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="25" ht="15">
       <c r="A25" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D25" s="2">
         <v>29495</v>
@@ -1893,17 +1949,20 @@
       </c>
       <c r="F25" s="1">
         <v>1</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="26" ht="15">
       <c r="A26" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D26" s="2">
         <v>29495</v>
@@ -1913,17 +1972,20 @@
       </c>
       <c r="F26" s="1">
         <v>1</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="27" ht="15">
       <c r="A27" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D27" s="2">
         <v>29495</v>
@@ -1933,17 +1995,20 @@
       </c>
       <c r="F27" s="1">
         <v>1</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="28" ht="15">
       <c r="A28" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D28" s="2">
         <v>29495</v>
@@ -1955,18 +2020,18 @@
         <v>1</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29" ht="15">
       <c r="A29" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D29" s="2">
         <v>29495</v>
@@ -1976,17 +2041,20 @@
       </c>
       <c r="F29" s="1">
         <v>1</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="30" ht="15">
       <c r="A30" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D30" s="2">
         <v>32874</v>
@@ -1998,18 +2066,18 @@
         <v>1</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="31" ht="15">
       <c r="A31" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D31" s="2">
         <v>32874</v>
@@ -2021,18 +2089,18 @@
         <v>1</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>67</v>
+        <v>43</v>
       </c>
     </row>
     <row r="32" ht="15">
       <c r="A32" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B32" t="s">
         <v>8</v>
       </c>
       <c r="C32" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D32" s="2">
         <v>29495</v>
@@ -2043,17 +2111,19 @@
       <c r="F32">
         <v>1</v>
       </c>
-      <c r="G32"/>
+      <c r="G32" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="33" ht="15">
       <c r="A33" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D33" s="2">
         <v>29495</v>
@@ -2063,17 +2133,20 @@
       </c>
       <c r="F33" s="1">
         <v>1</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="34" ht="15">
       <c r="A34" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D34" s="2">
         <v>29495</v>
@@ -2083,27 +2156,33 @@
       </c>
       <c r="F34" s="1">
         <v>1</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="35" ht="15">
       <c r="A35" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D35" s="2"/>
       <c r="E35" s="2"/>
+      <c r="G35" s="1" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="36" ht="15">
       <c r="A36" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D36" s="2">
         <v>32874</v>
@@ -2114,16 +2193,19 @@
       <c r="F36" s="1">
         <v>1</v>
       </c>
+      <c r="G36" s="1" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="37" ht="15">
       <c r="A37" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D37" s="2">
         <v>32874</v>
@@ -2135,18 +2217,18 @@
         <v>1</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>67</v>
+        <v>43</v>
       </c>
     </row>
     <row r="38" ht="15">
       <c r="A38" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D38" s="2">
         <v>32874</v>
@@ -2158,18 +2240,18 @@
         <v>1</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>67</v>
+        <v>43</v>
       </c>
     </row>
     <row r="39" ht="15">
       <c r="A39" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D39" s="2">
         <v>32874</v>
@@ -2180,16 +2262,19 @@
       <c r="F39" s="1">
         <v>1</v>
       </c>
+      <c r="G39" s="1" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="40" ht="15">
       <c r="A40" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D40" s="2">
         <v>29495</v>
@@ -2199,17 +2284,20 @@
       </c>
       <c r="F40" s="1">
         <v>1</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="41" ht="15">
       <c r="A41" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D41" s="2">
         <v>32874</v>
@@ -2220,16 +2308,19 @@
       <c r="F41" s="1">
         <v>1</v>
       </c>
+      <c r="G41" s="1" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="42" ht="15">
       <c r="A42" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D42" s="2">
         <v>34335</v>
@@ -2240,16 +2331,19 @@
       <c r="F42" s="1">
         <v>1</v>
       </c>
+      <c r="G42" s="1" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="43" ht="15">
       <c r="A43" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D43" s="2">
         <v>29495</v>
@@ -2259,30 +2353,33 @@
       </c>
       <c r="F43" s="1">
         <v>1</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="44" ht="15">
       <c r="A44" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D44" s="2"/>
       <c r="E44" s="2"/>
       <c r="G44" s="1" t="s">
-        <v>94</v>
+        <v>14</v>
       </c>
     </row>
     <row r="45" ht="15">
       <c r="A45" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D45" s="2">
         <v>29221</v>
@@ -2294,7 +2391,7 @@
         <v>1</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>97</v>
+        <v>14</v>
       </c>
     </row>
     <row r="46" ht="15">
@@ -2317,7 +2414,7 @@
         <v>1</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>97</v>
+        <v>14</v>
       </c>
     </row>
     <row r="47" ht="15">
@@ -2340,7 +2437,7 @@
         <v>1</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>97</v>
+        <v>14</v>
       </c>
     </row>
     <row r="48" ht="15">
@@ -2363,7 +2460,7 @@
         <v>1</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>97</v>
+        <v>14</v>
       </c>
     </row>
     <row r="49" ht="15">
@@ -2386,7 +2483,7 @@
         <v>1</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>97</v>
+        <v>14</v>
       </c>
     </row>
     <row r="50" ht="15">
@@ -2409,7 +2506,7 @@
         <v>1</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>97</v>
+        <v>14</v>
       </c>
     </row>
     <row r="51" ht="15">
@@ -2421,16 +2518,19 @@
       </c>
       <c r="D51" s="2"/>
       <c r="E51" s="2"/>
+      <c r="G51" s="1" t="s">
+        <v>110</v>
+      </c>
     </row>
     <row r="52" ht="15">
       <c r="A52" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D52" s="2">
         <v>32874</v>
@@ -2442,28 +2542,31 @@
         <v>1</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>97</v>
+        <v>110</v>
       </c>
     </row>
     <row r="53" ht="15">
       <c r="A53" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D53" s="2"/>
       <c r="E53" s="2"/>
+      <c r="G53" s="1" t="s">
+        <v>110</v>
+      </c>
     </row>
     <row r="54" ht="15">
       <c r="A54" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D54" s="2">
         <v>32874</v>
@@ -2474,16 +2577,19 @@
       <c r="F54" s="1">
         <v>1</v>
       </c>
+      <c r="G54" s="1" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="55" ht="15">
       <c r="A55" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D55" s="2">
         <v>34335</v>
@@ -2494,16 +2600,19 @@
       <c r="F55" s="1">
         <v>1</v>
       </c>
+      <c r="G55" s="1" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="56" ht="15">
       <c r="A56" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D56" s="2">
         <v>34335</v>
@@ -2514,16 +2623,19 @@
       <c r="F56" s="1">
         <v>1</v>
       </c>
+      <c r="G56" s="1" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="57" ht="15">
       <c r="A57" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D57" s="2">
         <v>32874</v>
@@ -2534,16 +2646,19 @@
       <c r="F57" s="1">
         <v>1</v>
       </c>
+      <c r="G57" s="1" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="58" ht="15">
       <c r="A58" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D58" s="2">
         <v>29495</v>
@@ -2553,17 +2668,20 @@
       </c>
       <c r="F58" s="1">
         <v>1</v>
+      </c>
+      <c r="G58" s="1" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="59" ht="15">
       <c r="A59" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D59" s="2">
         <v>32874</v>
@@ -2575,7 +2693,7 @@
         <v>1</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>126</v>
+        <v>91</v>
       </c>
     </row>
     <row r="60" ht="15">
@@ -2584,6 +2702,9 @@
       </c>
       <c r="D60" s="2"/>
       <c r="E60" s="2"/>
+      <c r="G60" s="1" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="61" ht="15">
       <c r="A61" s="1" t="s">
@@ -2605,7 +2726,7 @@
         <v>1</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>126</v>
+        <v>91</v>
       </c>
     </row>
     <row r="62" ht="15">
@@ -2628,18 +2749,18 @@
         <v>1</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>132</v>
+        <v>43</v>
       </c>
     </row>
     <row r="63" ht="15">
       <c r="A63" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C63" s="1" t="s">
         <v>133</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C63" s="1" t="s">
-        <v>134</v>
       </c>
       <c r="D63" s="2">
         <v>35065</v>
@@ -2651,18 +2772,18 @@
         <v>1</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>132</v>
+        <v>43</v>
       </c>
     </row>
     <row r="64" ht="15">
       <c r="A64" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C64" s="1" t="s">
         <v>135</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C64" s="1" t="s">
-        <v>136</v>
       </c>
       <c r="D64" s="2">
         <v>35065</v>
@@ -2674,18 +2795,18 @@
         <v>1</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>132</v>
+        <v>43</v>
       </c>
     </row>
     <row r="65" ht="15">
       <c r="A65" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C65" s="1" t="s">
         <v>137</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C65" s="1" t="s">
-        <v>138</v>
       </c>
       <c r="D65" s="2">
         <v>35065</v>
@@ -2697,18 +2818,18 @@
         <v>1</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>132</v>
+        <v>43</v>
       </c>
     </row>
     <row r="66" ht="15">
       <c r="A66" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C66" s="1" t="s">
         <v>139</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C66" s="1" t="s">
-        <v>140</v>
       </c>
       <c r="D66" s="2">
         <v>35065</v>
@@ -2720,18 +2841,18 @@
         <v>1</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>132</v>
+        <v>43</v>
       </c>
     </row>
     <row r="67" ht="15">
       <c r="A67" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C67" s="1" t="s">
         <v>141</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C67" s="1" t="s">
-        <v>142</v>
       </c>
       <c r="D67" s="2">
         <v>32874</v>
@@ -2743,18 +2864,18 @@
         <v>1</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>132</v>
+        <v>43</v>
       </c>
     </row>
     <row r="68" ht="15">
       <c r="A68" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C68" s="1" t="s">
         <v>143</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C68" s="1" t="s">
-        <v>144</v>
       </c>
       <c r="D68" s="2">
         <v>35065</v>
@@ -2766,18 +2887,18 @@
         <v>1</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>132</v>
+        <v>43</v>
       </c>
     </row>
     <row r="69" ht="15">
       <c r="A69" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C69" s="1" t="s">
         <v>145</v>
-      </c>
-      <c r="B69" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C69" s="1" t="s">
-        <v>146</v>
       </c>
       <c r="D69" s="2">
         <v>35065</v>
@@ -2789,18 +2910,18 @@
         <v>1</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>132</v>
+        <v>43</v>
       </c>
     </row>
     <row r="70" ht="15">
       <c r="A70" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C70" s="1" t="s">
         <v>147</v>
-      </c>
-      <c r="B70" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C70" s="1" t="s">
-        <v>148</v>
       </c>
       <c r="D70" s="2">
         <v>35065</v>
@@ -2812,18 +2933,18 @@
         <v>1</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>132</v>
+        <v>43</v>
       </c>
     </row>
     <row r="71" ht="15">
       <c r="A71" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C71" s="1" t="s">
         <v>149</v>
-      </c>
-      <c r="B71" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C71" s="1" t="s">
-        <v>150</v>
       </c>
       <c r="D71" s="2">
         <v>35065</v>
@@ -2835,18 +2956,18 @@
         <v>1</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>132</v>
+        <v>43</v>
       </c>
     </row>
     <row r="72" ht="15">
       <c r="A72" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C72" s="1" t="s">
         <v>151</v>
-      </c>
-      <c r="B72" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C72" s="1" t="s">
-        <v>152</v>
       </c>
       <c r="D72" s="2">
         <v>32874</v>
@@ -2857,16 +2978,19 @@
       <c r="F72" s="1">
         <v>1</v>
       </c>
+      <c r="G72" s="1" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="73" ht="15">
       <c r="A73" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C73" s="1" t="s">
         <v>153</v>
-      </c>
-      <c r="B73" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C73" s="1" t="s">
-        <v>154</v>
       </c>
       <c r="D73" s="2">
         <v>32874</v>
@@ -2877,44 +3001,59 @@
       <c r="F73" s="1">
         <v>1</v>
       </c>
+      <c r="G73" s="1" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="74" ht="15">
       <c r="C74" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D74" s="2"/>
       <c r="E74" s="2"/>
+      <c r="G74" s="1" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="75" ht="15">
       <c r="C75" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D75" s="2"/>
       <c r="E75" s="2"/>
+      <c r="G75" s="1" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="76" ht="15">
       <c r="C76" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D76" s="2"/>
       <c r="E76" s="2"/>
+      <c r="G76" s="1" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="77" ht="15">
       <c r="C77" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D77" s="2"/>
       <c r="E77" s="2"/>
+      <c r="G77" s="1" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="78" ht="15">
       <c r="A78" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C78" s="1" t="s">
         <v>159</v>
-      </c>
-      <c r="B78" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C78" s="1" t="s">
-        <v>160</v>
       </c>
       <c r="D78" s="2">
         <v>32874</v>
@@ -2925,23 +3064,29 @@
       <c r="F78" s="1">
         <v>1</v>
       </c>
+      <c r="G78" s="1" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="79" ht="15">
       <c r="C79" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D79" s="2"/>
       <c r="E79" s="2"/>
+      <c r="G79" s="1" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="80" ht="15">
       <c r="A80" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C80" s="1" t="s">
         <v>162</v>
-      </c>
-      <c r="B80" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C80" s="1" t="s">
-        <v>163</v>
       </c>
       <c r="D80" s="2">
         <v>32874</v>
@@ -2952,51 +3097,69 @@
       <c r="F80" s="1">
         <v>1</v>
       </c>
+      <c r="G80" s="1" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="81" ht="15">
       <c r="C81" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D81" s="2"/>
       <c r="E81" s="2"/>
+      <c r="G81" s="1" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="82" ht="15">
       <c r="C82" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D82" s="2"/>
       <c r="E82" s="2"/>
+      <c r="G82" s="1" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="83" ht="15">
       <c r="C83" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D83" s="2"/>
       <c r="E83" s="2"/>
+      <c r="G83" s="1" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="84" ht="15">
       <c r="C84" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D84" s="2"/>
       <c r="E84" s="2"/>
+      <c r="G84" s="1" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="85" ht="15">
       <c r="C85" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D85" s="2"/>
       <c r="E85" s="2"/>
+      <c r="G85" s="1" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="86" ht="15">
       <c r="A86" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C86" s="1" t="s">
         <v>169</v>
-      </c>
-      <c r="B86" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C86" s="1" t="s">
-        <v>170</v>
       </c>
       <c r="D86" s="2">
         <v>14793</v>
@@ -3007,16 +3170,19 @@
       <c r="F86" s="1">
         <v>1</v>
       </c>
+      <c r="G86" s="1" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="87" ht="15">
       <c r="A87" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C87" s="1" t="s">
         <v>171</v>
-      </c>
-      <c r="B87" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C87" s="1" t="s">
-        <v>172</v>
       </c>
       <c r="D87" s="2">
         <v>34335</v>
@@ -3027,16 +3193,19 @@
       <c r="F87" s="1">
         <v>1</v>
       </c>
+      <c r="G87" s="1" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="88" ht="15">
       <c r="A88" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C88" s="1" t="s">
         <v>173</v>
-      </c>
-      <c r="B88" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C88" s="1" t="s">
-        <v>174</v>
       </c>
       <c r="D88" s="2">
         <v>32874</v>
@@ -3048,18 +3217,18 @@
         <v>1</v>
       </c>
       <c r="G88" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="89" ht="15">
       <c r="A89" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C89" s="1" t="s">
         <v>175</v>
-      </c>
-      <c r="B89" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C89" s="1" t="s">
-        <v>176</v>
       </c>
       <c r="D89" s="2">
         <v>32874</v>
@@ -3071,18 +3240,18 @@
         <v>1</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="90" ht="15">
       <c r="A90" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C90" s="1" t="s">
         <v>177</v>
-      </c>
-      <c r="B90" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C90" s="1" t="s">
-        <v>178</v>
       </c>
       <c r="D90" s="2">
         <v>32874</v>
@@ -3094,18 +3263,18 @@
         <v>1</v>
       </c>
       <c r="G90" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="91" ht="15">
       <c r="A91" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C91" s="1" t="s">
         <v>179</v>
-      </c>
-      <c r="B91" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C91" s="1" t="s">
-        <v>180</v>
       </c>
       <c r="D91" s="2">
         <v>32874</v>
@@ -3117,18 +3286,18 @@
         <v>1</v>
       </c>
       <c r="G91" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="92" ht="15">
       <c r="A92" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C92" s="1" t="s">
         <v>181</v>
-      </c>
-      <c r="B92" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C92" s="1" t="s">
-        <v>182</v>
       </c>
       <c r="D92" s="2">
         <v>32874</v>
@@ -3140,18 +3309,18 @@
         <v>1</v>
       </c>
       <c r="G92" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="93" ht="15">
       <c r="A93" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C93" s="1" t="s">
         <v>183</v>
-      </c>
-      <c r="B93" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C93" s="1" t="s">
-        <v>184</v>
       </c>
       <c r="D93" s="2">
         <v>32874</v>
@@ -3163,18 +3332,18 @@
         <v>1</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="94" ht="15">
       <c r="A94" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C94" s="1" t="s">
         <v>185</v>
-      </c>
-      <c r="B94" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C94" s="1" t="s">
-        <v>186</v>
       </c>
       <c r="D94" s="2">
         <v>29952</v>
@@ -3186,18 +3355,18 @@
         <v>1</v>
       </c>
       <c r="G94" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="95" ht="15">
       <c r="A95" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C95" s="1" t="s">
         <v>187</v>
-      </c>
-      <c r="B95" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C95" s="1" t="s">
-        <v>188</v>
       </c>
       <c r="D95" s="2">
         <v>32874</v>
@@ -3209,18 +3378,18 @@
         <v>1</v>
       </c>
       <c r="G95" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="96" ht="15">
       <c r="A96" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C96" s="1" t="s">
         <v>189</v>
-      </c>
-      <c r="B96" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C96" s="1" t="s">
-        <v>190</v>
       </c>
       <c r="D96" s="2">
         <v>32874</v>
@@ -3232,18 +3401,18 @@
         <v>1</v>
       </c>
       <c r="G96" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="97" ht="15">
       <c r="A97" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C97" s="1" t="s">
         <v>191</v>
-      </c>
-      <c r="B97" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C97" s="1" t="s">
-        <v>192</v>
       </c>
       <c r="D97" s="2">
         <v>29221</v>
@@ -3255,18 +3424,18 @@
         <v>1</v>
       </c>
       <c r="G97" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="98" ht="15">
       <c r="A98" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C98" s="1" t="s">
         <v>193</v>
-      </c>
-      <c r="B98" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C98" s="1" t="s">
-        <v>194</v>
       </c>
       <c r="D98" s="2">
         <v>32874</v>
@@ -3278,18 +3447,18 @@
         <v>1</v>
       </c>
       <c r="G98" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="99" ht="15">
       <c r="A99" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C99" s="1" t="s">
         <v>195</v>
-      </c>
-      <c r="B99" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C99" s="1" t="s">
-        <v>196</v>
       </c>
       <c r="D99" s="2">
         <v>32874</v>
@@ -3301,18 +3470,18 @@
         <v>1</v>
       </c>
       <c r="G99" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="100" ht="15">
       <c r="A100" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C100" s="1" t="s">
         <v>197</v>
-      </c>
-      <c r="B100" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C100" s="1" t="s">
-        <v>198</v>
       </c>
       <c r="D100" s="2">
         <v>29221</v>
@@ -3324,18 +3493,18 @@
         <v>1</v>
       </c>
       <c r="G100" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="101" ht="15">
       <c r="A101" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C101" s="1" t="s">
         <v>199</v>
-      </c>
-      <c r="B101" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C101" s="1" t="s">
-        <v>200</v>
       </c>
       <c r="D101" s="2">
         <v>34213</v>
@@ -3346,17 +3515,20 @@
       <c r="F101" s="1">
         <v>1</v>
       </c>
+      <c r="G101" s="1" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="102" ht="15">
       <c r="A102" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C102" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="B102" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C102" s="1" t="s">
-        <v>202</v>
-      </c>
       <c r="D102" s="2">
         <v>29495</v>
       </c>
@@ -3365,17 +3537,20 @@
       </c>
       <c r="F102" s="1">
         <v>1</v>
+      </c>
+      <c r="G102" s="1" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="103" ht="15">
       <c r="A103" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C103" s="1" t="s">
         <v>203</v>
-      </c>
-      <c r="B103" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C103" s="1" t="s">
-        <v>204</v>
       </c>
       <c r="D103" s="2">
         <v>34213</v>
@@ -3386,16 +3561,19 @@
       <c r="F103" s="1">
         <v>1</v>
       </c>
+      <c r="G103" s="1" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="104" ht="15">
       <c r="A104" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C104" s="1" t="s">
         <v>205</v>
-      </c>
-      <c r="B104" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C104" s="1" t="s">
-        <v>206</v>
       </c>
       <c r="D104" s="2">
         <v>34213</v>
@@ -3406,17 +3584,20 @@
       <c r="F104" s="1">
         <v>1</v>
       </c>
+      <c r="G104" s="1" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="105" ht="15">
       <c r="A105" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C105" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="B105" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C105" s="1" t="s">
-        <v>208</v>
-      </c>
       <c r="D105" s="2">
         <v>29495</v>
       </c>
@@ -3425,18 +3606,21 @@
       </c>
       <c r="F105" s="1">
         <v>1</v>
+      </c>
+      <c r="G105" s="1" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="106" ht="15">
       <c r="A106" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C106" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="B106" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C106" s="1" t="s">
-        <v>210</v>
-      </c>
       <c r="D106" s="2">
         <v>29495</v>
       </c>
@@ -3445,18 +3629,21 @@
       </c>
       <c r="F106" s="1">
         <v>1</v>
+      </c>
+      <c r="G106" s="1" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="107" ht="15">
       <c r="A107" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C107" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="B107" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C107" s="1" t="s">
-        <v>212</v>
-      </c>
       <c r="D107" s="2">
         <v>29495</v>
       </c>
@@ -3465,18 +3652,21 @@
       </c>
       <c r="F107" s="1">
         <v>1</v>
+      </c>
+      <c r="G107" s="1" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="108" ht="15">
       <c r="A108" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C108" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="B108" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C108" s="1" t="s">
-        <v>214</v>
-      </c>
       <c r="D108" s="2">
         <v>29495</v>
       </c>
@@ -3485,18 +3675,21 @@
       </c>
       <c r="F108" s="1">
         <v>1</v>
+      </c>
+      <c r="G108" s="1" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="109" ht="15">
       <c r="A109" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C109" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="B109" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C109" s="1" t="s">
-        <v>216</v>
-      </c>
       <c r="D109" s="2">
         <v>29495</v>
       </c>
@@ -3505,18 +3698,21 @@
       </c>
       <c r="F109" s="1">
         <v>1</v>
+      </c>
+      <c r="G109" s="1" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="110" ht="15">
       <c r="A110" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C110" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="B110" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C110" s="1" t="s">
-        <v>218</v>
-      </c>
       <c r="D110" s="2">
         <v>29495</v>
       </c>
@@ -3525,18 +3721,21 @@
       </c>
       <c r="F110" s="1">
         <v>1</v>
+      </c>
+      <c r="G110" s="1" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="111" ht="15">
       <c r="A111" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C111" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="B111" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C111" s="1" t="s">
-        <v>220</v>
-      </c>
       <c r="D111" s="2">
         <v>29495</v>
       </c>
@@ -3545,18 +3744,21 @@
       </c>
       <c r="F111" s="1">
         <v>1</v>
+      </c>
+      <c r="G111" s="1" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="112" ht="15">
       <c r="A112" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C112" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="B112" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C112" s="1" t="s">
-        <v>222</v>
-      </c>
       <c r="D112" s="2">
         <v>29495</v>
       </c>
@@ -3565,18 +3767,21 @@
       </c>
       <c r="F112" s="1">
         <v>1</v>
+      </c>
+      <c r="G112" s="1" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="113" ht="15">
       <c r="A113" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C113" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="B113" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C113" s="1" t="s">
-        <v>224</v>
-      </c>
       <c r="D113" s="2">
         <v>29495</v>
       </c>
@@ -3585,18 +3790,21 @@
       </c>
       <c r="F113" s="1">
         <v>1</v>
+      </c>
+      <c r="G113" s="1" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="114" ht="15">
       <c r="A114" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C114" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="B114" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C114" s="1" t="s">
-        <v>226</v>
-      </c>
       <c r="D114" s="2">
         <v>29495</v>
       </c>
@@ -3605,18 +3813,21 @@
       </c>
       <c r="F114" s="1">
         <v>1</v>
+      </c>
+      <c r="G114" s="1" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="115" ht="15">
       <c r="A115" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="B115" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C115" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="B115" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C115" s="1" t="s">
-        <v>228</v>
-      </c>
       <c r="D115" s="2">
         <v>29495</v>
       </c>
@@ -3625,18 +3836,21 @@
       </c>
       <c r="F115" s="1">
         <v>1</v>
+      </c>
+      <c r="G115" s="1" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="116" ht="15">
       <c r="A116" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="B116" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C116" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="B116" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C116" s="1" t="s">
-        <v>230</v>
-      </c>
       <c r="D116" s="2">
         <v>29495</v>
       </c>
@@ -3645,18 +3859,21 @@
       </c>
       <c r="F116" s="1">
         <v>1</v>
+      </c>
+      <c r="G116" s="1" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="117" ht="15">
       <c r="A117" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C117" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="B117" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C117" s="1" t="s">
-        <v>232</v>
-      </c>
       <c r="D117" s="2">
         <v>29495</v>
       </c>
@@ -3665,18 +3882,21 @@
       </c>
       <c r="F117" s="1">
         <v>1</v>
+      </c>
+      <c r="G117" s="1" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="118" ht="15">
       <c r="A118" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C118" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="B118" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C118" s="1" t="s">
-        <v>234</v>
-      </c>
       <c r="D118" s="2">
         <v>29495</v>
       </c>
@@ -3685,18 +3905,21 @@
       </c>
       <c r="F118" s="1">
         <v>1</v>
+      </c>
+      <c r="G118" s="1" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="119" ht="15">
       <c r="A119" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="B119" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C119" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="B119" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C119" s="1" t="s">
-        <v>236</v>
-      </c>
       <c r="D119" s="2">
         <v>29495</v>
       </c>
@@ -3705,18 +3928,21 @@
       </c>
       <c r="F119" s="1">
         <v>1</v>
+      </c>
+      <c r="G119" s="1" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="120" ht="15">
       <c r="A120" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="B120" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C120" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="B120" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C120" s="1" t="s">
-        <v>238</v>
-      </c>
       <c r="D120" s="2">
         <v>29495</v>
       </c>
@@ -3725,18 +3951,21 @@
       </c>
       <c r="F120" s="1">
         <v>1</v>
+      </c>
+      <c r="G120" s="1" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="121" ht="15">
       <c r="A121" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="B121" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C121" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="B121" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C121" s="1" t="s">
-        <v>240</v>
-      </c>
       <c r="D121" s="2">
         <v>29495</v>
       </c>
@@ -3745,18 +3974,21 @@
       </c>
       <c r="F121" s="1">
         <v>1</v>
+      </c>
+      <c r="G121" s="1" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="122" ht="15">
       <c r="A122" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="B122" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C122" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="B122" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C122" s="1" t="s">
-        <v>242</v>
-      </c>
       <c r="D122" s="2">
         <v>29495</v>
       </c>
@@ -3765,18 +3997,21 @@
       </c>
       <c r="F122" s="1">
         <v>1</v>
+      </c>
+      <c r="G122" s="1" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="123" ht="15">
       <c r="A123" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="B123" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C123" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="B123" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C123" s="1" t="s">
-        <v>244</v>
-      </c>
       <c r="D123" s="2">
         <v>29495</v>
       </c>
@@ -3785,18 +4020,21 @@
       </c>
       <c r="F123" s="1">
         <v>1</v>
+      </c>
+      <c r="G123" s="1" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="124" ht="15">
       <c r="A124" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="B124" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C124" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="B124" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C124" s="1" t="s">
-        <v>246</v>
-      </c>
       <c r="D124" s="2">
         <v>29495</v>
       </c>
@@ -3805,18 +4043,21 @@
       </c>
       <c r="F124" s="1">
         <v>1</v>
+      </c>
+      <c r="G124" s="1" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="125" ht="15">
       <c r="A125" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="B125" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C125" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="B125" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C125" s="1" t="s">
-        <v>248</v>
-      </c>
       <c r="D125" s="2">
         <v>29495</v>
       </c>
@@ -3825,18 +4066,21 @@
       </c>
       <c r="F125" s="1">
         <v>1</v>
+      </c>
+      <c r="G125" s="1" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="126" ht="15">
       <c r="A126" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="B126" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C126" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="B126" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C126" s="1" t="s">
-        <v>250</v>
-      </c>
       <c r="D126" s="2">
         <v>29495</v>
       </c>
@@ -3845,17 +4089,20 @@
       </c>
       <c r="F126" s="1">
         <v>1</v>
+      </c>
+      <c r="G126" s="1" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="127" ht="15">
       <c r="A127" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C127" s="1" t="s">
         <v>251</v>
-      </c>
-      <c r="B127" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C127" s="1" t="s">
-        <v>252</v>
       </c>
       <c r="D127" s="2">
         <v>31107</v>
@@ -3866,16 +4113,19 @@
       <c r="F127" s="1">
         <v>1</v>
       </c>
+      <c r="G127" s="1" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="128" ht="15">
       <c r="A128" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="B128" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C128" s="1" t="s">
         <v>253</v>
-      </c>
-      <c r="B128" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C128" s="1" t="s">
-        <v>254</v>
       </c>
       <c r="D128" s="2">
         <v>32874</v>
@@ -3886,16 +4136,19 @@
       <c r="F128" s="1">
         <v>1</v>
       </c>
+      <c r="G128" s="1" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="129" ht="15">
       <c r="A129" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="B129" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C129" s="1" t="s">
         <v>255</v>
-      </c>
-      <c r="B129" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C129" s="1" t="s">
-        <v>256</v>
       </c>
       <c r="D129" s="2">
         <v>32874</v>
@@ -3906,16 +4159,19 @@
       <c r="F129" s="1">
         <v>1</v>
       </c>
+      <c r="G129" s="1" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="130" ht="15">
       <c r="A130" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B130" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C130" s="1" t="s">
         <v>257</v>
-      </c>
-      <c r="B130" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C130" s="1" t="s">
-        <v>258</v>
       </c>
       <c r="D130" s="2">
         <v>32874</v>
@@ -3926,16 +4182,19 @@
       <c r="F130" s="1">
         <v>1</v>
       </c>
+      <c r="G130" s="1" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="131" ht="15">
       <c r="A131" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B131" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C131" s="1" t="s">
         <v>259</v>
-      </c>
-      <c r="B131" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C131" s="1" t="s">
-        <v>260</v>
       </c>
       <c r="D131" s="2">
         <v>32874</v>
@@ -3946,16 +4205,19 @@
       <c r="F131" s="1">
         <v>1</v>
       </c>
+      <c r="G131" s="1" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="132" ht="15">
       <c r="A132" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="B132" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C132" s="1" t="s">
         <v>261</v>
-      </c>
-      <c r="B132" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C132" s="1" t="s">
-        <v>262</v>
       </c>
       <c r="D132" s="2">
         <v>35065</v>
@@ -3967,19 +4229,19 @@
         <v>1</v>
       </c>
       <c r="G132" s="1" t="s">
-        <v>132</v>
+        <v>43</v>
       </c>
     </row>
     <row r="133" ht="15">
       <c r="A133" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="B133" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C133" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="B133" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C133" s="1" t="s">
-        <v>264</v>
-      </c>
       <c r="D133" s="2">
         <v>29495</v>
       </c>
@@ -3990,29 +4252,32 @@
         <v>1</v>
       </c>
       <c r="G133" s="1" t="s">
-        <v>132</v>
+        <v>43</v>
       </c>
     </row>
     <row r="134" ht="15">
       <c r="A134" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="C134" s="1" t="s">
         <v>265</v>
-      </c>
-      <c r="C134" s="1" t="s">
-        <v>266</v>
       </c>
       <c r="D134" s="2"/>
       <c r="E134" s="2"/>
+      <c r="G134" s="1" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="135" ht="15">
       <c r="A135" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="B135" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C135" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="B135" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C135" s="1" t="s">
-        <v>268</v>
-      </c>
       <c r="D135" s="2">
         <v>29495</v>
       </c>
@@ -4021,18 +4286,21 @@
       </c>
       <c r="F135" s="1">
         <v>1</v>
+      </c>
+      <c r="G135" s="1" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="136" ht="15">
       <c r="A136" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="B136" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C136" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="B136" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C136" s="1" t="s">
-        <v>270</v>
-      </c>
       <c r="D136" s="2">
         <v>29495</v>
       </c>
@@ -4041,18 +4309,21 @@
       </c>
       <c r="F136" s="1">
         <v>1</v>
+      </c>
+      <c r="G136" s="1" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="137" ht="15">
       <c r="A137" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="B137" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C137" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="B137" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C137" s="1" t="s">
-        <v>272</v>
-      </c>
       <c r="D137" s="2">
         <v>29495</v>
       </c>
@@ -4061,18 +4332,21 @@
       </c>
       <c r="F137" s="1">
         <v>1</v>
+      </c>
+      <c r="G137" s="1" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="138" ht="15">
       <c r="A138" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="B138" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C138" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="B138" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C138" s="1" t="s">
-        <v>274</v>
-      </c>
       <c r="D138" s="2">
         <v>29495</v>
       </c>
@@ -4081,18 +4355,21 @@
       </c>
       <c r="F138" s="1">
         <v>1</v>
+      </c>
+      <c r="G138" s="1" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="139" ht="15">
       <c r="A139" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="B139" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C139" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="B139" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C139" s="1" t="s">
-        <v>276</v>
-      </c>
       <c r="D139" s="2">
         <v>29495</v>
       </c>
@@ -4101,18 +4378,21 @@
       </c>
       <c r="F139" s="1">
         <v>1</v>
+      </c>
+      <c r="G139" s="1" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="140" ht="15">
       <c r="A140" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="B140" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C140" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="B140" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C140" s="1" t="s">
-        <v>278</v>
-      </c>
       <c r="D140" s="2">
         <v>29495</v>
       </c>
@@ -4121,18 +4401,21 @@
       </c>
       <c r="F140" s="1">
         <v>1</v>
+      </c>
+      <c r="G140" s="1" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="141" ht="15">
       <c r="A141" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="B141" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C141" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="B141" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C141" s="1" t="s">
-        <v>280</v>
-      </c>
       <c r="D141" s="2">
         <v>29495</v>
       </c>
@@ -4141,30 +4424,36 @@
       </c>
       <c r="F141" s="1">
         <v>1</v>
+      </c>
+      <c r="G141" s="1" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="142" ht="13.800000000000001">
       <c r="A142" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="B142" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="B142" s="1" t="s">
+      <c r="C142" s="3" t="s">
         <v>282</v>
-      </c>
-      <c r="C142" s="3" t="s">
-        <v>283</v>
       </c>
       <c r="D142" s="2">
         <v>29190</v>
       </c>
       <c r="E142" s="2">
         <v>45657</v>
+      </c>
+      <c r="G142" s="4" t="s">
+        <v>283</v>
       </c>
     </row>
     <row r="143" ht="13.800000000000001">
       <c r="A143" s="3"/>
       <c r="C143" s="3"/>
       <c r="D143" s="2"/>
-      <c r="E143" s="4"/>
+      <c r="E143" s="5"/>
     </row>
     <row r="1048576" ht="12.800000000000001"/>
   </sheetData>
